--- a/04_output/P05/M05_Measure_Catalog.xlsx
+++ b/04_output/P05/M05_Measure_Catalog.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Measure_Catalog" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Measure_Catalog'!$A$1:$G$9</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -41,7 +39,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00123B5D"/>
+        <fgColor rgb="0017365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,7 +53,7 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00D7DEE8"/>
+        <color rgb="00D9E1F2"/>
       </bottom>
     </border>
   </borders>
@@ -433,21 +431,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="68" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="19.85" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="27.2" customWidth="1" min="4" max="4"/>
+    <col width="35.6" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Measure</t>
@@ -470,17 +468,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Sumber</t>
+          <t>Sumber utama</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner contoh</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Validasi minimum</t>
+          <t>Cara validasi minimum</t>
         </is>
       </c>
     </row>
@@ -502,7 +500,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Rp, 2 desimal</t>
+          <t>Currency (Rp), 2 desimal</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -517,7 +515,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>T0000001=Rp105,456.49; B001=Rp265,797,041.18</t>
+          <t>T0000001 = Rp105.456,49; B001 = Rp265.797.041,18</t>
         </is>
       </c>
     </row>
@@ -539,7 +537,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Rp, 2 desimal</t>
+          <t>Currency (Rp), 2 desimal</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -554,14 +552,14 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>T0000001=Rp62,400; B001=Rp180,456,800</t>
+          <t>T0000001 = Rp62.400,00; B001 = Rp180.456.800,00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Gross Profit P05</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -576,12 +574,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Rp, 2 desimal</t>
+          <t>Currency (Rp), 2 desimal</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Measures Sales &amp; Cost</t>
+          <t>Measure Total Sales &amp; Total Cost</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -591,34 +589,34 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Pastikan Sales-Cost=Gross Profit pada context sama</t>
+          <t>Pastikan Sales - Cost = Gross Profit di tiap context</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Profit Margin</t>
+          <t>Profit Margin P05</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Gross Profit sebagai proporsi Total Sales.</t>
+          <t>Gross Profit P05 sebagai persentase Total Sales.</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DIVIDE([Gross Profit],[Total Sales],0)</t>
+          <t>DIVIDE([Gross Profit P05], [Total Sales], 0)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>%, 2 desimal</t>
+          <t>Percentage, 2 desimal</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Gross Profit / Total Sales</t>
+          <t>Gross Profit P05 / Total Sales</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -628,7 +626,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>T0000001=40.83%; Jan 2024=31.75%</t>
+          <t>T0000001 = 40,83%; Jan 2024 = 31,75%</t>
         </is>
       </c>
     </row>
@@ -640,7 +638,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Jumlah Transaction_ID unik.</t>
+          <t>Jumlah unik Transaction_ID pada filter context aktif.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -665,7 +663,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>T0000001=1; B001=2,945</t>
+          <t>T0000001 = 1; B001 = 2.945</t>
         </is>
       </c>
     </row>
@@ -677,7 +675,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Jumlah Customer_ID unik nonblank.</t>
+          <t>Jumlah unik Customer_ID nonblank.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -702,7 +700,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Blank tidak dihitung; B001=943</t>
+          <t>Blank tidak dihitung; B001 = 943</t>
         </is>
       </c>
     </row>
@@ -714,17 +712,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Order dengan Return_Flag=Ya dibagi seluruh Orders.</t>
+          <t>Persentase order dengan Return_Flag = Ya terhadap seluruh Orders.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DIVIDE(CALCULATE([Orders], Fact_Sales[Return_Flag]="Ya"),[Orders],0)</t>
+          <t>DIVIDE(CALCULATE([Orders], 'Fact_Sales'[Return_Flag] = "Ya"), [Orders], 0)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>%, 2 desimal</t>
+          <t>Percentage, 2 desimal</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -739,7 +737,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>T0000001=0%; Jan 2024=2.78%</t>
+          <t>T0000001 = 0%; Jan 2024 = 2,78%</t>
         </is>
       </c>
     </row>
@@ -751,7 +749,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Rata-rata Satisfaction_Score yang terisi.</t>
+          <t>Rata-rata Satisfaction_Score terisi; blank tidak dimasukkan.</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -776,14 +774,11 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>T0000001=3.00; blank tetap dikecualikan</t>
+          <t>T0000001 = 3,00; blank tetap dikecualikan</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
-  <printOptions horizontalCentered="0"/>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>